--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.16668232261839</v>
+        <v>6.364585877425489</v>
       </c>
       <c r="D2" t="n">
-        <v>35.82097992265536</v>
+        <v>5.820909237431496</v>
       </c>
       <c r="E2" t="n">
-        <v>9.024364458089932</v>
+        <v>1.466459224439614</v>
       </c>
       <c r="F2" t="n">
-        <v>7.186376279670303</v>
+        <v>1.167786145446424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.27780168308206</v>
+        <v>3.457642773500835</v>
       </c>
       <c r="D3" t="n">
-        <v>18.31954818415521</v>
+        <v>2.976926579925222</v>
       </c>
       <c r="E3" t="n">
-        <v>9.024364458089932</v>
+        <v>1.466459224439614</v>
       </c>
       <c r="F3" t="n">
-        <v>7.186376279670303</v>
+        <v>1.167786145446424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.27011026802272</v>
+        <v>5.731392918553692</v>
       </c>
       <c r="D4" t="n">
-        <v>18.29980138917198</v>
+        <v>2.973717725740447</v>
       </c>
       <c r="E4" t="n">
-        <v>9.024364458089932</v>
+        <v>1.466459224439614</v>
       </c>
       <c r="F4" t="n">
-        <v>7.186376279670303</v>
+        <v>1.167786145446424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.98857990256727</v>
+        <v>7.473144234167182</v>
       </c>
       <c r="D5" t="n">
-        <v>22.45551157288562</v>
+        <v>3.649020630593913</v>
       </c>
       <c r="E5" t="n">
-        <v>9.024364458089932</v>
+        <v>1.466459224439614</v>
       </c>
       <c r="F5" t="n">
-        <v>7.186376279670303</v>
+        <v>1.167786145446424</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
